--- a/data/trans_orig/IP1005-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Provincia-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98530</t>
+          <t>98397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207163</t>
+          <t>206765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125514</t>
+          <t>125163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132260</t>
+          <t>131875</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260193</t>
+          <t>258919</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154323</t>
+          <t>154368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159233</t>
+          <t>158991</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>315385</t>
+          <t>316671</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321327</t>
+          <t>321355</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>675833</t>
+          <t>676357</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>717355</t>
+          <t>716681</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>722099</t>
+          <t>722098</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1395121</t>
+          <t>1395427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401905</t>
+          <t>1402375</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75525</t>
+          <t>75653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157736</t>
+          <t>157325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112015</t>
+          <t>112719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142222</t>
+          <t>142428</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281085</t>
+          <t>281086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161844</t>
+          <t>161405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167234</t>
+          <t>167940</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331373</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>437</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>701655</t>
+          <t>702025</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>706486</t>
+          <t>706491</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>744066</t>
+          <t>743397</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1448271</t>
+          <t>1447737</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1453945</t>
+          <t>1453967</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55026</t>
+          <t>54675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119578</t>
+          <t>119130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101152</t>
+          <t>100937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106923</t>
+          <t>106233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209740</t>
+          <t>210054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73379</t>
+          <t>73225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77918</t>
+          <t>77329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153777</t>
+          <t>153350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53946</t>
+          <t>53926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107746</t>
+          <t>108580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>544</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161768</t>
+          <t>161447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>165908</t>
+          <t>165873</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170303</t>
+          <t>170305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>328943</t>
+          <t>329665</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334475</t>
+          <t>334349</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>698404</t>
+          <t>698706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>703887</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>736743</t>
+          <t>736654</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>743375</t>
+          <t>743461</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1438180</t>
+          <t>1437660</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1445937</t>
+          <t>1446014</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1005-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1005-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3165</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3176</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3554</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100930</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>98397</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>97977</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>319</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206765</t>
+          <t>207143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2785,102 +2785,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3660</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3459</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3780</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4070</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5358</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>134976</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>131995</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>127948</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>125163</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>125251</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>134976</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>131875</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>381</t>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258919</t>
+          <t>260207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,72 +3123,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>162755</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>159831</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157262</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154368</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>154306</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>162755</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>158991</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>491</t>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>316671</t>
+          <t>316739</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321355</t>
+          <t>321364</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5742</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6019</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>720719</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>716907</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>722098</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679073</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>676357</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>680388</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>675279</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>680389</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>720719</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>716681</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>722098</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1395427</t>
+          <t>1395102</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402375</t>
+          <t>1402348</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4158,47 +4158,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5074,107 +5074,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2435</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2670</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5187,74 +5187,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77318</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75653</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>75061</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>225</t>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157325</t>
+          <t>157560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5760,107 +5760,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3975</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3522</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5873,74 +5873,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55291</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>52010</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>52463</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,76%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>93,71%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>161</t>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112719</t>
+          <t>112238</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6103,107 +6103,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3311</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3830</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3371</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -6216,72 +6216,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145067</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>142411</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145067</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>142428</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281086</t>
+          <t>280627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6451,102 +6451,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3375</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5484</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4686</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -6559,102 +6559,102 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170636</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167911</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164047</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>161405</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>160906</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170636</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167940</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>334683</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>330539</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>336023</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>334683</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>331337</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>336023</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4903</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>4745</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>746791</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>743418</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>705131</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>702025</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>706491</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>701744</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>706486</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>746791</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>743397</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2079</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1447737</t>
+          <t>1447882</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1453967</t>
+          <t>1453949</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7368,107 +7368,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>477</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2703</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -7486,69 +7486,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>56894</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54675</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54635</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>184</t>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119130</t>
+          <t>119433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7716,102 +7716,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>604</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3010</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3055</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4050</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4176</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -7824,74 +7824,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>109566</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>106628</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103343</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100937</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>100892</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>109566</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>106233</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>316</t>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210054</t>
+          <t>209622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8402,102 +8402,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3058</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>759</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3736</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4264</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3855</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4795</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -8510,74 +8510,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80540</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78126</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76202</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73225</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>72697</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>80540</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>77329</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153350</t>
+          <t>153482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8853,47 +8853,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9083,107 +9083,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>737</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>737</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3813</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4071</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3432</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -9196,72 +9196,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57002</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>53834</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>93,24%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57002</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>53926</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108580</t>
+          <t>107941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9769,72 +9769,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1774</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5084</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>479</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2729</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2558</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4976</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -9882,74 +9882,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>169075</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>165765</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170303</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>163697</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>161447</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>161618</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>169075</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>165873</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>170305</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>512</t>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>329665</t>
+          <t>329689</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334349</t>
+          <t>334475</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,72 +10112,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>8470</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2319</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5665</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5496</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8190</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -10225,72 +10225,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>740972</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>736374</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>743485</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>702052</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>698706</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>703887</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>698875</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>703766</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,93%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>740972</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>736654</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>743461</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1437660</t>
+          <t>1438318</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1446014</t>
+          <t>1446161</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
